--- a/Deliverables/BOM/Sensor-Board/eSpark-BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/eSpark-BOM-Sensor-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E64D2E-07E3-4418-9C44-2729F6B96C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6971AF30-D0DD-4850-AC1D-4AE8EA0F1474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
   <si>
     <t>Component list</t>
   </si>
@@ -167,12 +167,6 @@
     <t>Cap-0402</t>
   </si>
   <si>
-    <t>AFC07-S32FCA-00_</t>
-  </si>
-  <si>
-    <t>FH34SRJ-12S-0.5SH(50)_</t>
-  </si>
-  <si>
     <t>Res-0402</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t>Solder Bridge</t>
   </si>
   <si>
-    <t>TC-0522C-1.7-260G_</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
@@ -332,9 +323,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
     <t>LCSC</t>
   </si>
   <si>
@@ -354,6 +342,9 @@
   </si>
   <si>
     <t>ArmBand-Sensor-Board</t>
+  </si>
+  <si>
+    <t>Custom</t>
   </si>
 </sst>
 </file>
@@ -1043,6 +1034,15 @@
     <xf numFmtId="165" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1074,15 +1074,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1460,15 +1451,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="75"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1479,7 +1470,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="53" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1504,7 +1495,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="54" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1518,7 +1509,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="76"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1529,7 +1520,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="55" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1543,7 +1534,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="77"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1568,7 +1559,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="77"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1589,7 +1580,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="77"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1610,7 +1601,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="77"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1631,7 +1622,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="77"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1651,43 +1642,43 @@
         <v>41</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>88</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1696,7 +1687,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="71" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -1709,19 +1700,19 @@
         <v>42</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -1734,7 +1725,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P10" s="38">
         <v>2.3400000000000001E-2</v>
@@ -1752,7 +1743,7 @@
         <f t="shared" ref="B11:B20" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="72" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="51" t="s">
@@ -1765,19 +1756,19 @@
         <v>43</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L11" s="51">
         <v>2</v>
@@ -1790,7 +1781,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="65" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P11" s="52">
         <v>8.3000000000000001E-3</v>
@@ -1808,7 +1799,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="71" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -1818,22 +1809,22 @@
         <v>31</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -1846,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P12" s="62">
         <v>0.16900000000000001</v>
@@ -1864,7 +1855,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="72" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="51" t="s">
@@ -1874,20 +1865,20 @@
         <v>32</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I13" s="51"/>
       <c r="J13" s="51" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -1900,7 +1891,7 @@
         <v>3</v>
       </c>
       <c r="O13" s="63" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P13" s="62">
         <v>0.19689999999999999</v>
@@ -1918,32 +1909,32 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="83" t="s">
-        <v>97</v>
+      <c r="C14" s="73" t="s">
+        <v>94</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>12</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L14" s="58">
         <v>13</v>
@@ -1953,16 +1944,16 @@
         <v>26</v>
       </c>
       <c r="N14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O14" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q14" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R14" s="58"/>
       <c r="S14" s="60"/>
@@ -1973,7 +1964,7 @@
         <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="71" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="37" t="s">
@@ -1983,20 +1974,20 @@
         <v>34</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I15" s="37"/>
       <c r="J15" s="37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L15" s="37">
         <v>2</v>
@@ -2009,7 +2000,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="66" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P15" s="67">
         <v>5.9999999999999995E-4</v>
@@ -2027,7 +2018,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="72" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="51" t="s">
@@ -2037,22 +2028,22 @@
         <v>35</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I16" s="51" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J16" s="51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L16" s="51">
         <v>2</v>
@@ -2065,7 +2056,7 @@
         <v>50</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P16" s="62">
         <v>1.47E-2</v>
@@ -2083,8 +2074,8 @@
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="83" t="s">
-        <v>48</v>
+      <c r="C17" s="73" t="s">
+        <v>46</v>
       </c>
       <c r="D17" s="58" t="s">
         <v>23</v>
@@ -2093,22 +2084,22 @@
         <v>36</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G17" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L17" s="58">
         <v>6</v>
@@ -2118,16 +2109,16 @@
         <v>12</v>
       </c>
       <c r="N17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O17" s="58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q17" s="59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R17" s="58"/>
       <c r="S17" s="60"/>
@@ -2138,7 +2129,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="82" t="s">
+      <c r="C18" s="72" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="51" t="s">
@@ -2148,22 +2139,22 @@
         <v>37</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="G18" s="51" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H18" s="51" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I18" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J18" s="51" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L18" s="51">
         <v>2</v>
@@ -2176,7 +2167,7 @@
         <v>50</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P18" s="62">
         <v>1.61E-2</v>
@@ -2194,7 +2185,7 @@
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="C19" s="71" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="37" t="s">
@@ -2204,22 +2195,22 @@
         <v>38</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L19" s="37">
         <v>1</v>
@@ -2232,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="O19" s="64" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P19" s="38">
         <v>0.94820000000000004</v>
@@ -2250,7 +2241,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="72" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="51" t="s">
@@ -2260,22 +2251,22 @@
         <v>39</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G20" s="51" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H20" s="51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I20" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J20" s="51" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L20" s="51">
         <v>1</v>
@@ -2288,7 +2279,7 @@
         <v>3</v>
       </c>
       <c r="O20" s="63" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P20" s="62">
         <v>0.46779999999999999</v>
@@ -2306,7 +2297,7 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="81" t="s">
+      <c r="C21" s="71" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -2316,22 +2307,22 @@
         <v>40</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -2344,7 +2335,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="69" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P21" s="70">
         <v>0.14219999999999999</v>
@@ -2370,17 +2361,17 @@
       <c r="K22" s="45"/>
       <c r="L22" s="45"/>
       <c r="M22" s="45"/>
-      <c r="N22" s="79" t="s">
+      <c r="N22" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
       <c r="Q22" s="48">
         <f>SUM(Q10:Q21)</f>
         <v>8.9547000000000008</v>
       </c>
-      <c r="R22" s="75"/>
-      <c r="S22" s="76"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="79"/>
     </row>
     <row r="23" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2396,17 +2387,17 @@
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
-      <c r="N23" s="79" t="s">
+      <c r="N23" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="O23" s="80"/>
-      <c r="P23" s="80"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
       <c r="Q23" s="49">
         <f>Q22/2</f>
         <v>4.4773500000000004</v>
       </c>
-      <c r="R23" s="77"/>
-      <c r="S23" s="78"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="5">
